--- a/static/posh/MyPosh.xlsx
+++ b/static/posh/MyPosh.xlsx
@@ -22,19 +22,19 @@
     <t>Address</t>
   </si>
   <si>
-    <t>Direct Employees</t>
-  </si>
-  <si>
     <t>No. of Direct Employees</t>
   </si>
   <si>
-    <t>Vendor</t>
-  </si>
-  <si>
     <t>No. of Vendors</t>
   </si>
   <si>
-    <t>Total No. of Employees</t>
+    <t>Direct Employee</t>
+  </si>
+  <si>
+    <t>Vendors</t>
+  </si>
+  <si>
+    <t>Total Number of Indirect Employees</t>
   </si>
 </sst>
 </file>
@@ -126,28 +126,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -457,16 +436,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
@@ -477,12 +456,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D1048576">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$C2&lt;&gt;"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F1048576">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2&lt;&gt;"Yes"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/static/posh/MyPosh.xlsx
+++ b/static/posh/MyPosh.xlsx
@@ -14,34 +14,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Location Name</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>No. of Direct Employees</t>
-  </si>
-  <si>
-    <t>No. of Vendors</t>
-  </si>
-  <si>
-    <t>Direct Employee</t>
-  </si>
-  <si>
-    <t>Vendors</t>
-  </si>
-  <si>
-    <t>Total Number of Indirect Employees</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>SR.NO</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>ADDRESS</t>
+  </si>
+  <si>
+    <t>DO YOU HAVE DIRECT EMPLOYEES (YES/NO)</t>
+  </si>
+  <si>
+    <t>NUMBER OF DIRECT EMPLOYEES</t>
+  </si>
+  <si>
+    <t>DO YOU HAVE VENDORS (YES/NO)</t>
+  </si>
+  <si>
+    <t>NUMBER OF VENDORS</t>
+  </si>
+  <si>
+    <t>TOTAL / MAX NUMBER OF EMPLOYEES DEPLOYED BY VENDORS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -50,15 +53,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -73,12 +82,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -101,11 +109,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -113,17 +150,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -417,71 +458,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="11.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" style="2" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22" style="5" customWidth="1"/>
-    <col min="4" max="4" width="24" style="2" customWidth="1"/>
-    <col min="5" max="7" width="22" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31" style="4" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.42578125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="11.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C2" s="2"/>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="D2" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D1048576">
+  <conditionalFormatting sqref="E2:E1048576">
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$C2&lt;&gt;"Yes"</formula>
+      <formula>$D2&lt;&gt;"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F1048576">
+  <conditionalFormatting sqref="G2:G1048576">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$E2&lt;&gt;"Yes"</formula>
+      <formula>$F2&lt;&gt;"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="7">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Only &quot;Yes&quot; or &quot;No&quot; are accepted. Please correct your entry." promptTitle="Allowed Values" prompt="Please enter &quot;Yes&quot; or &quot;No&quot; only." sqref="E3:E1048576 C5:C1048576">
+  <dataValidations count="5">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Only &quot;Yes&quot; or &quot;No&quot; are accepted. Please correct your entry." promptTitle="Allowed Values" prompt="Please enter &quot;Yes&quot; or &quot;No&quot; only." sqref="D2:D1048576 F2:F1048576">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Only &quot;Yes&quot; or &quot;No&quot; are accepted. Please correct your entry." promptTitle="Allowed Values" prompt="Please enter &quot;Yes&quot; or &quot;No&quot; only." sqref="E2">
-      <formula1>"Yes, No"</formula1>
+    <dataValidation errorTitle="Invalid Entry" error="Only &quot;Yes&quot; or &quot;No&quot; are accepted. Please correct your entry." promptTitle="Allowed Values" prompt="Please enter &quot;Yes&quot; or &quot;No&quot; only." sqref="F1 D1"/>
+    <dataValidation errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="E1"/>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="E2:E1048576">
+      <formula1>AND(ISNUMBER(E2), $D2="Yes")</formula1>
     </dataValidation>
-    <dataValidation errorTitle="Invalid Entry" error="Only &quot;Yes&quot; or &quot;No&quot; are accepted. Please correct your entry." promptTitle="Allowed Values" prompt="Please enter &quot;Yes&quot; or &quot;No&quot; only." sqref="E1 C1"/>
-    <dataValidation errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="D1"/>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="D2:D1048576">
-      <formula1>AND(ISNUMBER(D2), $C2="Yes")</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="F1:F1048576">
-      <formula1>AND(ISNUMBER(F1), $E1="Yes")</formula1>
-    </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Only &quot;Yes&quot; or &quot;No&quot; are accepted. Please correct your entry." promptTitle="Allowed Values" prompt="Please enter &quot;Yes&quot; or &quot;No&quot; only." sqref="C2:C4">
-      <formula1>"Yes, No"</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="G1:G1048576">
+      <formula1>AND(ISNUMBER(G1), $F1="Yes")</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/static/posh/MyPosh.xlsx
+++ b/static/posh/MyPosh.xlsx
@@ -142,7 +142,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -153,21 +153,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -461,59 +471,64 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="11.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" style="6" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="51.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31" style="4" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31" style="7" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.42578125" style="6" customWidth="1"/>
     <col min="9" max="16384" width="11.28515625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
-      <c r="D2" s="2"/>
+      <c r="D2" s="6"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E1048576">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$D2&lt;&gt;"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1048576">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$F2&lt;&gt;"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H1048576">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$F2&lt;&gt;"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="7">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Only &quot;Yes&quot; or &quot;No&quot; are accepted. Please correct your entry." promptTitle="Allowed Values" prompt="Please enter &quot;Yes&quot; or &quot;No&quot; only." sqref="D2:D1048576 F2:F1048576">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
@@ -522,8 +537,14 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="E2:E1048576">
       <formula1>AND(ISNUMBER(E2), $D2="Yes")</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="G1:G1048576">
-      <formula1>AND(ISNUMBER(G1), $F1="Yes")</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="G3:G1048576">
+      <formula1>AND(ISNUMBER(G3), $F3="Yes")</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="G2">
+      <formula1>AND(ISNUMBER(G2), $F2="Yes")</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="This field only accepts numbers if the Direct Employees is &quot;Yes.&quot; Please correct your entry." promptTitle="Enter Number &gt; 0" prompt="Please enter a whole number only if the Direct Employees is &quot;Yes&quot;. Leave blank if &quot;No&quot; is selected." sqref="H2:H1048576">
+      <formula1>AND(ISNUMBER(H2), $F2="Yes")</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
